--- a/Checklists/LLR_review_checklist.xlsx
+++ b/Checklists/LLR_review_checklist.xlsx
@@ -43,9 +43,6 @@
     <t>LLR are generally written into small workable pieces so later we can easily divide into function.</t>
   </si>
   <si>
-    <t>LLR should be written in such a manner that for next phase it is clear to design ex.- module design or unit design.</t>
-  </si>
-  <si>
     <t>SCADE or STATE flow should be as per guideline, all GATES, FLIPFLOP there syntax and block diagram should be mentioned, better if Truth Table also present.</t>
   </si>
   <si>
@@ -59,6 +56,9 @@
   </si>
   <si>
     <t>LLR should be clear and detailed so we can understand easily.</t>
+  </si>
+  <si>
+    <t>LLR should be written in such a manner that for next phase it is clear to design ex. module design or unit design.</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -455,7 +455,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -463,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -471,7 +471,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="43.2">
@@ -479,7 +479,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8">
@@ -487,7 +487,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8">
